--- a/BLL/new.xlsx
+++ b/BLL/new.xlsx
@@ -8,27 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Pictures\תכנות\שנה ב\פוריקט שנתי\C#\פרויקט חדש 20.04\Gym_Api\BLL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251AA1BC-67BA-441B-B801-8F9044AF0591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E18932-8CF0-4778-9155-3B245B3BE77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="797" firstSheet="3" activeTab="12" xr2:uid="{587815B1-586A-4800-8953-55F13164A91A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="898" firstSheet="1" activeTab="14" xr2:uid="{587815B1-586A-4800-8953-55F13164A91A}"/>
   </bookViews>
   <sheets>
-    <sheet name="MuscleType (2)" sheetId="17" r:id="rId1"/>
+    <sheet name="MuscleType (2)" sheetId="17" state="hidden" r:id="rId1"/>
     <sheet name="MuscleType" sheetId="16" r:id="rId2"/>
     <sheet name="NeedSubMuscle" sheetId="18" r:id="rId3"/>
-    <sheet name="List1 (2)" sheetId="13" r:id="rId4"/>
-    <sheet name="List" sheetId="1" r:id="rId5"/>
+    <sheet name="List1 (2)" sheetId="13" state="hidden" r:id="rId4"/>
+    <sheet name="List" sheetId="1" state="hidden" r:id="rId5"/>
     <sheet name="Amount" sheetId="8" r:id="rId6"/>
-    <sheet name="גיליון1" sheetId="11" r:id="rId7"/>
+    <sheet name="גיליון1" sheetId="11" state="hidden" r:id="rId7"/>
     <sheet name="MuscleSize" sheetId="6" r:id="rId8"/>
     <sheet name="Size" sheetId="5" r:id="rId9"/>
-    <sheet name="TimeForCategory1" sheetId="10" r:id="rId10"/>
+    <sheet name="TimeForCategory1" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="Repeat" sheetId="9" r:id="rId11"/>
     <sheet name="TimeForCategory" sheetId="2" r:id="rId12"/>
     <sheet name="List1" sheetId="12" r:id="rId13"/>
     <sheet name="Equipment" sheetId="14" r:id="rId14"/>
     <sheet name="OrderList" sheetId="19" r:id="rId15"/>
-    <sheet name="גיליון2" sheetId="15" r:id="rId16"/>
+    <sheet name="גיליון2" sheetId="15" state="hidden" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="61">
   <si>
     <t>רגליים</t>
   </si>
@@ -759,7 +759,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6D77C5D-CC62-422B-B731-211177640110}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -964,6 +964,91 @@
       </c>
       <c r="E12">
         <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
+        <v>90</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>90</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>90</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>90</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>90</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F923399F-C972-4C66-B8A4-12BE28FF010B}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.59765625" customWidth="1"/>
@@ -1241,6 +1326,91 @@
         <v>40</v>
       </c>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>40</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1248,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DD0EDE-1A13-4DA2-A472-0AD55A18B868}">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2653,6 +2823,622 @@
         <v>0</v>
       </c>
       <c r="R25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>4</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>2</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>2</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>2</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
         <v>1</v>
       </c>
     </row>
@@ -4937,7 +5723,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A7414C-2518-439C-B3E9-3FAAF40161C8}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.796875" customWidth="1"/>
@@ -5776,6 +6562,414 @@
         <v>4</v>
       </c>
     </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>40</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>40</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>40</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>40</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>40</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>40</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>40</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>40</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>40</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>40</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>40</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>40</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>40</v>
+      </c>
+      <c r="B71" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>40</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>40</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5783,7 +6977,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D777455-EB31-4228-8ADB-DB45891FB62D}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6617,6 +7811,414 @@
       </c>
       <c r="E49">
         <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>40</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>40</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>40</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>40</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>40</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>40</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>40</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>40</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>40</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>40</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>40</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>40</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>40</v>
+      </c>
+      <c r="B71" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>40</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>40</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
